--- a/F_grouping/reference/usable_factors.xlsx
+++ b/F_grouping/reference/usable_factors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
   <si>
     <t>factor_id</t>
   </si>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -946,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>0.5</v>
@@ -955,7 +955,7 @@
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -976,33 +976,33 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>0.528125</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -1026,15 +1026,15 @@
         <v>3</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>0.5291666666666666</v>
+        <v>0.528125</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1073,15 +1073,15 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>0.5062500000000001</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         <v>0.5</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -1105,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1117,24 +1117,24 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
-        <v>0.5145833333333332</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0.5</v>
@@ -1143,7 +1143,7 @@
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1161,39 +1161,39 @@
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>0.5083333333333333</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>2</v>
@@ -1217,15 +1217,15 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <v>0.4885416666666666</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1255,24 +1255,24 @@
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>2</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>0.5010416666666667</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1305,30 +1305,30 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>0.53125</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1358,30 +1358,30 @@
         <v>3</v>
       </c>
       <c r="O16">
-        <v>0.4895833333333333</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1399,33 +1399,33 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17">
         <v>3</v>
       </c>
       <c r="O17">
-        <v>0.4989583333333333</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -1434,30 +1434,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>0.5510416666666668</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1487,39 +1487,39 @@
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>0.525</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1540,33 +1540,33 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>0.5291666666666667</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1575,10 +1575,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -1590,18 +1590,18 @@
         <v>4</v>
       </c>
       <c r="N21">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>0.509375</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1625,42 +1625,42 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <v>3</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O22">
-        <v>0.4947916666666666</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1681,21 +1681,21 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O23">
-        <v>0.490625</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1704,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1719,27 +1719,27 @@
         <v>0</v>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>3</v>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>0.484375</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1748,13 +1748,13 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1772,21 +1772,21 @@
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>0.4927083333333334</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1828,27 +1828,27 @@
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>0.5291666666666667</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1866,27 +1866,27 @@
         <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27">
         <v>4</v>
       </c>
       <c r="O27">
-        <v>0.4885416666666667</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1895,13 +1895,13 @@
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -1913,21 +1913,21 @@
         <v>0</v>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
-        <v>0.4614583333333333</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1966,15 +1966,15 @@
         <v>3</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>0.5229166666666666</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -2010,33 +2010,33 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>0.4916666666666666</v>
+        <v>0.4614583333333333</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -2054,21 +2054,21 @@
         <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O31">
-        <v>0.4947916666666667</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2101,21 +2101,21 @@
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>0.5072916666666666</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0.5</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -2154,30 +2154,30 @@
         <v>2</v>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O33">
-        <v>0.5062500000000001</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0.5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -2201,21 +2201,21 @@
         <v>3</v>
       </c>
       <c r="N34">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>0.5083333333333334</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0.5</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -2242,27 +2242,27 @@
         <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35">
         <v>3.5</v>
       </c>
       <c r="O35">
-        <v>0.5083333333333334</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0.5</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -2289,36 +2289,36 @@
         <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N36">
         <v>3.5</v>
       </c>
       <c r="O36">
-        <v>0.4958333333333334</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0.5</v>
       </c>
       <c r="E37">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -2336,36 +2336,36 @@
         <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
-        <v>0.4916666666666667</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -2377,42 +2377,42 @@
         <v>0</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O38">
-        <v>0.478125</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -2430,36 +2430,36 @@
         <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39">
         <v>4</v>
       </c>
       <c r="O39">
-        <v>0.4770833333333333</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2480,33 +2480,33 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>0.4958333333333334</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -2530,21 +2530,21 @@
         <v>3</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O41">
-        <v>0.4979166666666666</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>0.5</v>
@@ -2562,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -2574,18 +2574,18 @@
         <v>1</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42">
-        <v>0.5052083333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>2</v>
       </c>
       <c r="G43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -2627,12 +2627,12 @@
         <v>5</v>
       </c>
       <c r="O43">
-        <v>0.5354166666666667</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -2665,21 +2665,21 @@
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>0.5020833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2688,16 +2688,16 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2718,18 +2718,18 @@
         <v>3</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45">
-        <v>0.5114583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2741,16 +2741,16 @@
         <v>0.5</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -2765,21 +2765,21 @@
         <v>3</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>0.5</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0.5</v>
@@ -2806,21 +2806,21 @@
         <v>0</v>
       </c>
       <c r="L47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O47">
-        <v>0.5302083333333333</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2829,16 +2829,16 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -2859,21 +2859,21 @@
         <v>3</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
-        <v>0.5062500000000001</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0.5</v>
@@ -2882,7 +2882,7 @@
         <v>0.5</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -2906,21 +2906,21 @@
         <v>3</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O49">
-        <v>0.5302083333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -2947,21 +2947,21 @@
         <v>0</v>
       </c>
       <c r="L50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50">
-        <v>0.4885416666666666</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3008,28 +3008,28 @@
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0.5</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -3041,27 +3041,27 @@
         <v>0</v>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O52">
-        <v>0.4875</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0.5</v>
@@ -3097,15 +3097,15 @@
         <v>4</v>
       </c>
       <c r="O53">
-        <v>0.4864583333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>0.5</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -3138,21 +3138,21 @@
         <v>1</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O54">
-        <v>0.525</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3161,19 +3161,19 @@
         <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
       <c r="H55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -3182,27 +3182,27 @@
         <v>0</v>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>0.525</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0.5</v>
@@ -3211,7 +3211,7 @@
         <v>0.5</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -3235,21 +3235,21 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O56">
-        <v>0.5083333333333333</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0.5</v>
@@ -3258,7 +3258,7 @@
         <v>0.5</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -3276,21 +3276,21 @@
         <v>0</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O57">
-        <v>0.515625</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -3326,24 +3326,24 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O58">
-        <v>0.521875</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0.5</v>
@@ -3352,7 +3352,7 @@
         <v>0.5</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -3370,27 +3370,27 @@
         <v>0</v>
       </c>
       <c r="L59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O59">
-        <v>0.4927083333333333</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>0.5</v>
@@ -3399,7 +3399,7 @@
         <v>0.5</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -3420,18 +3420,18 @@
         <v>1</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O60">
-        <v>0.4916666666666666</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3464,27 +3464,27 @@
         <v>0</v>
       </c>
       <c r="L61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O61">
-        <v>0.509375</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>0.5</v>
@@ -3493,7 +3493,7 @@
         <v>0.5</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -3517,18 +3517,18 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
-        <v>0.503125</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3540,7 +3540,7 @@
         <v>0.5</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
@@ -3558,21 +3558,21 @@
         <v>0</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O63">
-        <v>0.5104166666666667</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -3614,18 +3614,18 @@
         <v>4</v>
       </c>
       <c r="O64">
-        <v>0.5177083333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0.5</v>
@@ -3652,21 +3652,21 @@
         <v>0</v>
       </c>
       <c r="L65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O65">
-        <v>0.4958333333333333</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -3708,12 +3708,12 @@
         <v>6</v>
       </c>
       <c r="O66">
-        <v>0.4802083333333333</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -3746,24 +3746,24 @@
         <v>0</v>
       </c>
       <c r="L67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O67">
-        <v>0.521875</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>0.5</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -3793,27 +3793,27 @@
         <v>0</v>
       </c>
       <c r="L68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68">
         <v>4</v>
       </c>
-      <c r="N68">
-        <v>7</v>
-      </c>
       <c r="O68">
-        <v>0.521875</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0.5</v>
@@ -3822,7 +3822,7 @@
         <v>0.5</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
@@ -3846,21 +3846,21 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69">
-        <v>0.4927083333333333</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0.5</v>
@@ -3869,7 +3869,7 @@
         <v>0.5</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -3887,27 +3887,27 @@
         <v>0</v>
       </c>
       <c r="L70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70">
+        <v>2</v>
+      </c>
+      <c r="N70">
         <v>4</v>
       </c>
-      <c r="N70">
-        <v>5</v>
-      </c>
       <c r="O70">
-        <v>0.5052083333333334</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>0.5</v>
@@ -3916,7 +3916,7 @@
         <v>0.5</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -3940,21 +3940,21 @@
         <v>3</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O71">
-        <v>0.4875</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0.5</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -3987,56 +3987,291 @@
         <v>3</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72">
-        <v>0.4989583333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>0.5</v>
+      </c>
+      <c r="E73">
+        <v>0.5</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>4</v>
+      </c>
+      <c r="N73">
+        <v>7</v>
+      </c>
+      <c r="O73">
+        <v>0.521875</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>0.5</v>
+      </c>
+      <c r="E74">
+        <v>0.5</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74">
+        <v>0.4927083333333333</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0.5</v>
+      </c>
+      <c r="E75">
+        <v>0.5</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75">
+        <v>0.5052083333333334</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0.5</v>
+      </c>
+      <c r="E76">
+        <v>0.5</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76">
+        <v>5</v>
+      </c>
+      <c r="O76">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0.5</v>
+      </c>
+      <c r="E77">
+        <v>0.5</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>3</v>
+      </c>
+      <c r="N77">
+        <v>5</v>
+      </c>
+      <c r="O77">
+        <v>0.4989583333333334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
         <v>86</v>
       </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>0.5</v>
-      </c>
-      <c r="E73">
-        <v>0.5</v>
-      </c>
-      <c r="F73">
-        <v>3</v>
-      </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="b">
-        <v>1</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73">
-        <v>3</v>
-      </c>
-      <c r="N73">
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>0.5</v>
+      </c>
+      <c r="E78">
+        <v>0.5</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>3</v>
+      </c>
+      <c r="N78">
         <v>6</v>
       </c>
-      <c r="O73">
+      <c r="O78">
         <v>0.5114583333333333</v>
       </c>
     </row>

--- a/F_grouping/reference/usable_factors.xlsx
+++ b/F_grouping/reference/usable_factors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>factor_id</t>
   </si>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -987,22 +987,22 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -1026,15 +1026,15 @@
         <v>3</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>0.528125</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1073,15 +1073,15 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>0.5291666666666666</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         <v>0.5</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -1105,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1117,24 +1117,24 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>0.5062500000000001</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>0.5</v>
@@ -1143,7 +1143,7 @@
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1161,39 +1161,39 @@
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
         <v>4</v>
       </c>
-      <c r="N12">
-        <v>5</v>
-      </c>
       <c r="O12">
-        <v>0.5145833333333332</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>2</v>
@@ -1217,15 +1217,15 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <v>0.5083333333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1255,24 +1255,24 @@
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>2</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
-        <v>0.4885416666666666</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1305,30 +1305,30 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>0.5010416666666667</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1358,30 +1358,30 @@
         <v>3</v>
       </c>
       <c r="O16">
-        <v>0.53125</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1399,33 +1399,33 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17">
         <v>3</v>
       </c>
       <c r="O17">
-        <v>0.4895833333333333</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -1434,30 +1434,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>0.4989583333333333</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1487,39 +1487,39 @@
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>0.5510416666666668</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1540,33 +1540,33 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>0.53125</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1575,10 +1575,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -1590,18 +1590,18 @@
         <v>4</v>
       </c>
       <c r="N21">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O21">
-        <v>0.525</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1625,42 +1625,42 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>3</v>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>0.5291666666666667</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1681,21 +1681,21 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>0.509375</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1704,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1719,27 +1719,27 @@
         <v>0</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>3</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>0.4947916666666666</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1748,13 +1748,13 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1772,21 +1772,21 @@
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O25">
-        <v>0.490625</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1828,27 +1828,27 @@
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>0.484375</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1866,27 +1866,27 @@
         <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27">
         <v>4</v>
       </c>
       <c r="O27">
-        <v>0.4927083333333334</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1895,13 +1895,13 @@
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -1913,21 +1913,21 @@
         <v>0</v>
       </c>
       <c r="L28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>0.5291666666666667</v>
+        <v>0.4614583333333333</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1966,15 +1966,15 @@
         <v>3</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>0.4885416666666667</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30">
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -2010,33 +2010,33 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>0.4614583333333333</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -2054,21 +2054,21 @@
         <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>0.5229166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2101,21 +2101,21 @@
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>0.4916666666666666</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0.5</v>
       </c>
       <c r="E33">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -2154,30 +2154,30 @@
         <v>2</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O33">
-        <v>0.4947916666666667</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0.5</v>
       </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -2201,21 +2201,21 @@
         <v>3</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O34">
-        <v>0.5072916666666666</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0.5</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -2242,27 +2242,27 @@
         <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35">
         <v>3.5</v>
       </c>
       <c r="O35">
-        <v>0.5062500000000001</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0.5</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -2289,36 +2289,36 @@
         <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36">
         <v>3.5</v>
       </c>
       <c r="O36">
-        <v>0.5083333333333334</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0.5</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F37">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -2336,36 +2336,36 @@
         <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O37">
-        <v>0.5083333333333334</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -2377,42 +2377,42 @@
         <v>0</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>0.4958333333333334</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -2430,36 +2430,36 @@
         <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39">
         <v>4</v>
       </c>
       <c r="O39">
-        <v>0.4916666666666667</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2480,33 +2480,33 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>0.478125</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -2530,15 +2530,15 @@
         <v>3</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>0.4770833333333333</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2580,12 +2580,12 @@
         <v>5</v>
       </c>
       <c r="O42">
-        <v>0.4958333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>2</v>
       </c>
       <c r="G43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -2627,12 +2627,12 @@
         <v>5</v>
       </c>
       <c r="O43">
-        <v>0.4979166666666666</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -2665,21 +2665,21 @@
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44">
+        <v>2</v>
+      </c>
+      <c r="N44">
         <v>4</v>
       </c>
-      <c r="N44">
-        <v>6</v>
-      </c>
       <c r="O44">
-        <v>0.5052083333333334</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2688,16 +2688,16 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2718,18 +2718,18 @@
         <v>3</v>
       </c>
       <c r="N45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O45">
-        <v>0.5052083333333334</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2741,16 +2741,16 @@
         <v>0.5</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -2765,21 +2765,21 @@
         <v>3</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>0.5354166666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0.5</v>
@@ -2806,21 +2806,21 @@
         <v>0</v>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O47">
-        <v>0.5020833333333333</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2829,16 +2829,16 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -2859,21 +2859,21 @@
         <v>3</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O48">
-        <v>0.5114583333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0.5</v>
@@ -2882,7 +2882,7 @@
         <v>0.5</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -2906,21 +2906,21 @@
         <v>3</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49">
-        <v>0.5</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -2947,21 +2947,21 @@
         <v>0</v>
       </c>
       <c r="L50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O50">
-        <v>0.5302083333333333</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3008,28 +3008,28 @@
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0.5</v>
       </c>
       <c r="E52">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -3041,27 +3041,27 @@
         <v>0</v>
       </c>
       <c r="L52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>0.5302083333333333</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>0.5</v>
@@ -3097,15 +3097,15 @@
         <v>4</v>
       </c>
       <c r="O53">
-        <v>0.4885416666666666</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>0.5</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -3138,21 +3138,21 @@
         <v>1</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O54">
-        <v>0.5062500000000001</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3161,19 +3161,19 @@
         <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F55">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -3182,27 +3182,27 @@
         <v>0</v>
       </c>
       <c r="L55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O55">
-        <v>0.4875</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0.5</v>
@@ -3211,7 +3211,7 @@
         <v>0.5</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -3235,21 +3235,21 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O56">
-        <v>0.4864583333333333</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0.5</v>
@@ -3258,7 +3258,7 @@
         <v>0.5</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -3276,21 +3276,21 @@
         <v>0</v>
       </c>
       <c r="L57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57">
+        <v>2</v>
+      </c>
+      <c r="N57">
         <v>4</v>
       </c>
-      <c r="N57">
-        <v>7</v>
-      </c>
       <c r="O57">
-        <v>0.525</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -3326,24 +3326,24 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O58">
-        <v>0.51875</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0.5</v>
@@ -3352,7 +3352,7 @@
         <v>0.5</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -3370,27 +3370,27 @@
         <v>0</v>
       </c>
       <c r="L59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59">
         <v>4</v>
       </c>
-      <c r="N59">
-        <v>7</v>
-      </c>
       <c r="O59">
-        <v>0.525</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0.5</v>
@@ -3399,7 +3399,7 @@
         <v>0.5</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -3420,18 +3420,18 @@
         <v>1</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O60">
-        <v>0.51875</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3464,27 +3464,27 @@
         <v>0</v>
       </c>
       <c r="L61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O61">
-        <v>0.5083333333333333</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0.5</v>
@@ -3493,7 +3493,7 @@
         <v>0.5</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -3517,18 +3517,18 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O62">
-        <v>0.515625</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3540,7 +3540,7 @@
         <v>0.5</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
@@ -3558,21 +3558,21 @@
         <v>0</v>
       </c>
       <c r="L63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O63">
-        <v>0.521875</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -3614,18 +3614,18 @@
         <v>4</v>
       </c>
       <c r="O64">
-        <v>0.4927083333333333</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0.5</v>
@@ -3652,21 +3652,21 @@
         <v>0</v>
       </c>
       <c r="L65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O65">
-        <v>0.4916666666666666</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -3708,12 +3708,12 @@
         <v>6</v>
       </c>
       <c r="O66">
-        <v>0.509375</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -3746,24 +3746,24 @@
         <v>0</v>
       </c>
       <c r="L67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O67">
-        <v>0.503125</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>0.5</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -3793,27 +3793,27 @@
         <v>0</v>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O68">
-        <v>0.5104166666666667</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0.5</v>
@@ -3822,7 +3822,7 @@
         <v>0.5</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
@@ -3846,21 +3846,21 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69">
-        <v>0.5177083333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0.5</v>
@@ -3869,7 +3869,7 @@
         <v>0.5</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -3887,27 +3887,27 @@
         <v>0</v>
       </c>
       <c r="L70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70">
-        <v>0.4958333333333333</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0.5</v>
@@ -3916,7 +3916,7 @@
         <v>0.5</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -3940,21 +3940,21 @@
         <v>3</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O71">
-        <v>0.4802083333333333</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0.5</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -3987,15 +3987,15 @@
         <v>3</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O72">
-        <v>0.521875</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -4019,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -4031,247 +4031,12 @@
         <v>1</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O73">
-        <v>0.521875</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
-      <c r="A74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
-        <v>0.5</v>
-      </c>
-      <c r="E74">
-        <v>0.5</v>
-      </c>
-      <c r="F74">
-        <v>3</v>
-      </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="b">
-        <v>1</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>2</v>
-      </c>
-      <c r="N74">
-        <v>5</v>
-      </c>
-      <c r="O74">
-        <v>0.4927083333333333</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
-      <c r="A75" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>0.5</v>
-      </c>
-      <c r="E75">
-        <v>0.5</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" t="b">
-        <v>1</v>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75">
-        <v>4</v>
-      </c>
-      <c r="N75">
-        <v>5</v>
-      </c>
-      <c r="O75">
-        <v>0.5052083333333334</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
-      <c r="A76" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>0.5</v>
-      </c>
-      <c r="E76">
-        <v>0.5</v>
-      </c>
-      <c r="F76">
-        <v>2</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="b">
-        <v>1</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" t="b">
-        <v>1</v>
-      </c>
-      <c r="M76">
-        <v>3</v>
-      </c>
-      <c r="N76">
-        <v>5</v>
-      </c>
-      <c r="O76">
-        <v>0.4875</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
-      <c r="A77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
-        <v>0.5</v>
-      </c>
-      <c r="E77">
-        <v>0.5</v>
-      </c>
-      <c r="F77">
-        <v>2</v>
-      </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" t="b">
-        <v>1</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" t="b">
-        <v>1</v>
-      </c>
-      <c r="M77">
-        <v>3</v>
-      </c>
-      <c r="N77">
-        <v>5</v>
-      </c>
-      <c r="O77">
-        <v>0.4989583333333334</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="A78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>0.5</v>
-      </c>
-      <c r="E78">
-        <v>0.5</v>
-      </c>
-      <c r="F78">
-        <v>3</v>
-      </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" t="b">
-        <v>1</v>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" t="b">
-        <v>1</v>
-      </c>
-      <c r="M78">
-        <v>3</v>
-      </c>
-      <c r="N78">
-        <v>6</v>
-      </c>
-      <c r="O78">
         <v>0.5114583333333333</v>
       </c>
     </row>

--- a/F_grouping/reference/usable_factors.xlsx
+++ b/F_grouping/reference/usable_factors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>factor_id</t>
   </si>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2773,13 +2773,13 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0.5</v>
@@ -2788,7 +2788,7 @@
         <v>0.5</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -2812,21 +2812,21 @@
         <v>3</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O47">
-        <v>0.5302083333333333</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0.5</v>
@@ -2835,7 +2835,7 @@
         <v>0.5</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -2859,21 +2859,21 @@
         <v>3</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
-        <v>0.5062500000000001</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0.5</v>
@@ -2909,18 +2909,18 @@
         <v>5</v>
       </c>
       <c r="O49">
-        <v>0.5302083333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -2947,21 +2947,21 @@
         <v>0</v>
       </c>
       <c r="L50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50">
-        <v>0.4885416666666666</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2994,21 +2994,21 @@
         <v>0</v>
       </c>
       <c r="L51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O51">
-        <v>0.5062500000000001</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3020,16 +3020,16 @@
         <v>0.5</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -3041,42 +3041,42 @@
         <v>0</v>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O52">
-        <v>0.4875</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0.5</v>
       </c>
       <c r="E53">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -3091,24 +3091,24 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>0.4864583333333333</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0.5</v>
@@ -3117,7 +3117,7 @@
         <v>0.5</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -3135,21 +3135,21 @@
         <v>0</v>
       </c>
       <c r="L54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54">
+        <v>2</v>
+      </c>
+      <c r="N54">
         <v>4</v>
       </c>
-      <c r="N54">
-        <v>7</v>
-      </c>
       <c r="O54">
-        <v>0.51875</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -3196,7 +3196,7 @@
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -3229,27 +3229,27 @@
         <v>0</v>
       </c>
       <c r="L56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56">
-        <v>0.5083333333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0.5</v>
@@ -3258,7 +3258,7 @@
         <v>0.5</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -3276,21 +3276,21 @@
         <v>0</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O57">
-        <v>0.515625</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -3332,18 +3332,18 @@
         <v>6</v>
       </c>
       <c r="O58">
-        <v>0.521875</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0.5</v>
@@ -3352,7 +3352,7 @@
         <v>0.5</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -3376,15 +3376,15 @@
         <v>2</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59">
-        <v>0.4927083333333333</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -3417,21 +3417,21 @@
         <v>0</v>
       </c>
       <c r="L60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60">
-        <v>0.4916666666666666</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3473,18 +3473,18 @@
         <v>6</v>
       </c>
       <c r="O61">
-        <v>0.509375</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>0.5</v>
@@ -3493,7 +3493,7 @@
         <v>0.5</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -3517,21 +3517,21 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
-        <v>0.503125</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0.5</v>
@@ -3558,27 +3558,27 @@
         <v>0</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O63">
-        <v>0.5104166666666667</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0.5</v>
@@ -3587,7 +3587,7 @@
         <v>0.5</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
@@ -3605,24 +3605,24 @@
         <v>0</v>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O64">
-        <v>0.5177083333333334</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -3634,7 +3634,7 @@
         <v>0.5</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" t="b">
         <v>1</v>
@@ -3658,18 +3658,18 @@
         <v>2</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O65">
-        <v>0.4958333333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0.5</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
@@ -3699,27 +3699,27 @@
         <v>0</v>
       </c>
       <c r="L66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O66">
-        <v>0.4802083333333333</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0.5</v>
@@ -3728,7 +3728,7 @@
         <v>0.5</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
@@ -3746,24 +3746,24 @@
         <v>0</v>
       </c>
       <c r="L67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O67">
-        <v>0.521875</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>0.5</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -3793,21 +3793,21 @@
         <v>0</v>
       </c>
       <c r="L68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68">
         <v>4</v>
       </c>
-      <c r="N68">
-        <v>7</v>
-      </c>
       <c r="O68">
-        <v>0.521875</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -3840,27 +3840,27 @@
         <v>0</v>
       </c>
       <c r="L69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O69">
-        <v>0.4927083333333333</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0.5</v>
@@ -3869,7 +3869,7 @@
         <v>0.5</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -3890,24 +3890,24 @@
         <v>1</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O70">
-        <v>0.5052083333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>0.5</v>
@@ -3916,7 +3916,7 @@
         <v>0.5</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -3925,7 +3925,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -3937,24 +3937,24 @@
         <v>1</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O71">
-        <v>0.4875</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0.5</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -3981,62 +3981,203 @@
         <v>0</v>
       </c>
       <c r="L72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72">
         <v>5</v>
       </c>
       <c r="O72">
-        <v>0.4989583333333334</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0.5</v>
+      </c>
+      <c r="E73">
+        <v>0.5</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>4</v>
+      </c>
+      <c r="N73">
+        <v>5</v>
+      </c>
+      <c r="O73">
+        <v>0.5052083333333334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0.5</v>
+      </c>
+      <c r="E74">
+        <v>0.5</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>3</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0.5</v>
+      </c>
+      <c r="E75">
+        <v>0.5</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>3</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75">
+        <v>0.4989583333333334</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
         <v>86</v>
       </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>0.5</v>
-      </c>
-      <c r="E73">
-        <v>0.5</v>
-      </c>
-      <c r="F73">
-        <v>3</v>
-      </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="b">
-        <v>1</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73">
-        <v>3</v>
-      </c>
-      <c r="N73">
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>0.5</v>
+      </c>
+      <c r="E76">
+        <v>0.5</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76">
         <v>6</v>
       </c>
-      <c r="O73">
+      <c r="O76">
         <v>0.5114583333333333</v>
       </c>
     </row>

--- a/F_grouping/reference/usable_factors.xlsx
+++ b/F_grouping/reference/usable_factors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
   <si>
     <t>factor_id</t>
   </si>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2820,13 +2820,13 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0.5</v>
@@ -2835,7 +2835,7 @@
         <v>0.5</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -2859,18 +2859,18 @@
         <v>3</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O48">
-        <v>0.5302083333333333</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2882,7 +2882,7 @@
         <v>0.5</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -2906,21 +2906,21 @@
         <v>3</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O49">
-        <v>0.5062500000000001</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2994,21 +2994,21 @@
         <v>0</v>
       </c>
       <c r="L51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O51">
-        <v>0.4885416666666666</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3050,12 +3050,12 @@
         <v>5</v>
       </c>
       <c r="O52">
-        <v>0.5062500000000001</v>
+        <v>0.4645833333333334</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3067,16 +3067,16 @@
         <v>0.5</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -3091,24 +3091,24 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="O53">
-        <v>0.4875</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0.5</v>
@@ -3144,15 +3144,15 @@
         <v>4</v>
       </c>
       <c r="O54">
-        <v>0.4864583333333333</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         <v>0.5</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -3185,24 +3185,24 @@
         <v>1</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O55">
-        <v>0.51875</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0.5</v>
@@ -3211,7 +3211,7 @@
         <v>0.5</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -3235,18 +3235,18 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56">
-        <v>0.4927083333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -3258,7 +3258,7 @@
         <v>0.5</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -3276,24 +3276,24 @@
         <v>0</v>
       </c>
       <c r="L57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57">
+        <v>2</v>
+      </c>
+      <c r="N57">
         <v>4</v>
       </c>
-      <c r="N57">
-        <v>7</v>
-      </c>
       <c r="O57">
-        <v>0.51875</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -3305,7 +3305,7 @@
         <v>0.5</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
@@ -3329,18 +3329,18 @@
         <v>3</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O58">
-        <v>0.4927083333333334</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3349,16 +3349,16 @@
         <v>0.5</v>
       </c>
       <c r="E59">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -3373,18 +3373,18 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>0.5083333333333333</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -3426,12 +3426,12 @@
         <v>4</v>
       </c>
       <c r="O60">
-        <v>0.515625</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -3467,24 +3467,24 @@
         <v>1</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O61">
-        <v>0.521875</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0.5</v>
@@ -3493,7 +3493,7 @@
         <v>0.5</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -3511,27 +3511,27 @@
         <v>0</v>
       </c>
       <c r="L62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O62">
-        <v>0.4927083333333333</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0.5</v>
@@ -3540,7 +3540,7 @@
         <v>0.5</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
@@ -3564,15 +3564,15 @@
         <v>3</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O63">
-        <v>0.4916666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -3614,12 +3614,12 @@
         <v>6</v>
       </c>
       <c r="O64">
-        <v>0.509375</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -3652,24 +3652,24 @@
         <v>0</v>
       </c>
       <c r="L65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O65">
-        <v>0.503125</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0.5</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
@@ -3690,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -3699,27 +3699,27 @@
         <v>0</v>
       </c>
       <c r="L66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O66">
-        <v>0.5104166666666667</v>
+        <v>0.51875</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0.5</v>
@@ -3728,7 +3728,7 @@
         <v>0.5</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
@@ -3746,24 +3746,24 @@
         <v>0</v>
       </c>
       <c r="L67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O67">
-        <v>0.5177083333333334</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>0.5</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
@@ -3793,21 +3793,21 @@
         <v>0</v>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O68">
-        <v>0.4958333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -3849,12 +3849,12 @@
         <v>6</v>
       </c>
       <c r="O69">
-        <v>0.4802083333333333</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -3896,12 +3896,12 @@
         <v>6</v>
       </c>
       <c r="O70">
-        <v>0.521875</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -3925,7 +3925,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -3934,27 +3934,27 @@
         <v>0</v>
       </c>
       <c r="L71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O71">
-        <v>0.521875</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0.5</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -3987,21 +3987,21 @@
         <v>2</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O72">
-        <v>0.4927083333333333</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0.5</v>
@@ -4010,7 +4010,7 @@
         <v>0.5</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
@@ -4019,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -4031,18 +4031,18 @@
         <v>1</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73">
-        <v>0.5052083333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -4075,21 +4075,21 @@
         <v>0</v>
       </c>
       <c r="L74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74">
-        <v>0.4875</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -4131,12 +4131,12 @@
         <v>5</v>
       </c>
       <c r="O75">
-        <v>0.4989583333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -4178,6 +4178,570 @@
         <v>6</v>
       </c>
       <c r="O76">
+        <v>0.509375</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>0.5</v>
+      </c>
+      <c r="E77">
+        <v>0.5</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>5</v>
+      </c>
+      <c r="O77">
+        <v>0.503125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>0.5</v>
+      </c>
+      <c r="E78">
+        <v>0.5</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>2</v>
+      </c>
+      <c r="N78">
+        <v>4</v>
+      </c>
+      <c r="O78">
+        <v>0.5104166666666667</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0.5</v>
+      </c>
+      <c r="E79">
+        <v>0.5</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>4</v>
+      </c>
+      <c r="O79">
+        <v>0.5177083333333334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>0.5</v>
+      </c>
+      <c r="E80">
+        <v>0.5</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>4</v>
+      </c>
+      <c r="O80">
+        <v>0.4958333333333333</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>0.5</v>
+      </c>
+      <c r="E81">
+        <v>0.5</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="b">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>6</v>
+      </c>
+      <c r="O81">
+        <v>0.4802083333333333</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>0.5</v>
+      </c>
+      <c r="E82">
+        <v>0.5</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="b">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <v>6</v>
+      </c>
+      <c r="O82">
+        <v>0.521875</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>0.5</v>
+      </c>
+      <c r="E83">
+        <v>0.5</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>7</v>
+      </c>
+      <c r="O83">
+        <v>0.521875</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>0.5</v>
+      </c>
+      <c r="E84">
+        <v>0.5</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>5</v>
+      </c>
+      <c r="O84">
+        <v>0.4927083333333333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0.5</v>
+      </c>
+      <c r="E85">
+        <v>0.5</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="b">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>5</v>
+      </c>
+      <c r="O85">
+        <v>0.5052083333333334</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0.5</v>
+      </c>
+      <c r="E86">
+        <v>0.5</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="b">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>5</v>
+      </c>
+      <c r="O86">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0.5</v>
+      </c>
+      <c r="E87">
+        <v>0.5</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="b">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>3</v>
+      </c>
+      <c r="N87">
+        <v>5</v>
+      </c>
+      <c r="O87">
+        <v>0.4989583333333334</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>0.5</v>
+      </c>
+      <c r="E88">
+        <v>0.5</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="b">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>3</v>
+      </c>
+      <c r="N88">
+        <v>6</v>
+      </c>
+      <c r="O88">
         <v>0.5114583333333333</v>
       </c>
     </row>

--- a/F_grouping/reference/usable_factors.xlsx
+++ b/F_grouping/reference/usable_factors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="89">
   <si>
     <t>factor_id</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>V018</t>
+  </si>
+  <si>
+    <t>V023</t>
+  </si>
+  <si>
+    <t>V024</t>
   </si>
   <si>
     <t>W001</t>
@@ -606,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -987,22 +993,22 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -1011,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1023,18 +1029,18 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>0.5291666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1043,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1073,15 +1079,15 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>0.5062500000000001</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1090,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -1105,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1117,33 +1123,33 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>0.5145833333333332</v>
+        <v>0.5291666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0.5</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1161,45 +1167,45 @@
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O12">
-        <v>0.5083333333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1211,18 +1217,18 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>0.4885416666666666</v>
+        <v>0.5145833333333332</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1231,13 +1237,13 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1261,15 +1267,15 @@
         <v>2</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>0.5010416666666667</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1302,21 +1308,21 @@
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>0.53125</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1325,16 +1331,16 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1352,24 +1358,24 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
-        <v>0.4895833333333333</v>
+        <v>0.5010416666666667</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1378,10 +1384,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1390,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1399,21 +1405,21 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17">
         <v>3</v>
       </c>
       <c r="O17">
-        <v>0.4989583333333333</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1425,54 +1431,54 @@
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>0.5510416666666668</v>
+        <v>0.4895833333333333</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -1481,45 +1487,45 @@
         <v>1</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>0.53125</v>
+        <v>0.4989583333333333</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -1528,45 +1534,45 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>0.5291666666666667</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1575,45 +1581,45 @@
         <v>1</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>0.509375</v>
+        <v>0.5510416666666668</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1622,30 +1628,30 @@
         <v>1</v>
       </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>0.4947916666666666</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1669,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -1681,18 +1687,18 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>0.490625</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1734,15 +1740,15 @@
         <v>3.5</v>
       </c>
       <c r="O24">
-        <v>0.484375</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1751,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1766,30 +1772,30 @@
         <v>0</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O25">
-        <v>0.4927083333333334</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1798,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1813,33 +1819,33 @@
         <v>0</v>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O26">
-        <v>0.5291666666666667</v>
+        <v>0.4947916666666666</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -1848,7 +1854,7 @@
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1872,21 +1878,21 @@
         <v>3</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>0.4885416666666667</v>
+        <v>0.490625</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1895,13 +1901,13 @@
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -1913,27 +1919,27 @@
         <v>0</v>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
-        <v>0.4614583333333333</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1942,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1960,36 +1966,36 @@
         <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>0.5229166666666666</v>
+        <v>0.4927083333333334</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -2007,27 +2013,27 @@
         <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O30">
-        <v>0.4916666666666666</v>
+        <v>0.5291666666666667</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0.5</v>
@@ -2036,7 +2042,7 @@
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -2054,21 +2060,21 @@
         <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31">
         <v>4</v>
       </c>
       <c r="O31">
-        <v>0.4947916666666667</v>
+        <v>0.4885416666666667</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2077,19 +2083,19 @@
         <v>1</v>
       </c>
       <c r="D32">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -2101,36 +2107,36 @@
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O32">
-        <v>0.5072916666666666</v>
+        <v>0.4614583333333333</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -2148,36 +2154,36 @@
         <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O33">
-        <v>0.5062500000000001</v>
+        <v>0.5229166666666666</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0.5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -2195,36 +2201,36 @@
         <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>0.5083333333333334</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0.5</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F35">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -2242,21 +2248,21 @@
         <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O35">
-        <v>0.5083333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2268,10 +2274,10 @@
         <v>0.5</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F36">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -2289,21 +2295,21 @@
         <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>0.4958333333333334</v>
+        <v>0.5072916666666666</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2315,10 +2321,10 @@
         <v>0.5</v>
       </c>
       <c r="E37">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -2342,30 +2348,30 @@
         <v>2</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
-        <v>0.4916666666666667</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -2377,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2386,33 +2392,33 @@
         <v>1</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O38">
-        <v>0.478125</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -2436,15 +2442,15 @@
         <v>3</v>
       </c>
       <c r="N39">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O39">
-        <v>0.4770833333333333</v>
+        <v>0.5083333333333334</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2456,10 +2462,10 @@
         <v>0.5</v>
       </c>
       <c r="E40">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -2477,13 +2483,13 @@
         <v>0</v>
       </c>
       <c r="L40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O40">
         <v>0.4958333333333334</v>
@@ -2491,7 +2497,7 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2524,36 +2530,36 @@
         <v>0</v>
       </c>
       <c r="L41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O41">
-        <v>0.4979166666666666</v>
+        <v>0.4916666666666667</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
@@ -2565,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -2574,42 +2580,42 @@
         <v>1</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42">
         <v>5</v>
       </c>
       <c r="O42">
-        <v>0.5052083333333334</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -2624,15 +2630,15 @@
         <v>3</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43">
-        <v>0.5354166666666667</v>
+        <v>0.4770833333333333</v>
       </c>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2665,21 +2671,21 @@
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44">
-        <v>0.5020833333333333</v>
+        <v>0.4958333333333334</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2688,16 +2694,16 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2706,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2718,18 +2724,18 @@
         <v>3</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45">
-        <v>0.5114583333333333</v>
+        <v>0.4979166666666666</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2741,7 +2747,7 @@
         <v>0.5</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
@@ -2765,18 +2771,18 @@
         <v>3</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>0.5</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2788,7 +2794,7 @@
         <v>0.5</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -2812,18 +2818,18 @@
         <v>3</v>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O47">
-        <v>0.4958333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2835,16 +2841,16 @@
         <v>0.5</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -2859,18 +2865,18 @@
         <v>3</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48">
-        <v>0.4958333333333334</v>
+        <v>0.5354166666666667</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2882,7 +2888,7 @@
         <v>0.5</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -2900,21 +2906,21 @@
         <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>0.4875</v>
+        <v>0.5020833333333333</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2923,16 +2929,16 @@
         <v>1</v>
       </c>
       <c r="D50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2941,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -2953,18 +2959,18 @@
         <v>3</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O50">
-        <v>0.5302083333333333</v>
+        <v>0.5114583333333333</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2976,7 +2982,7 @@
         <v>0.5</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
@@ -3000,10 +3006,10 @@
         <v>3</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O51">
-        <v>0.465625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -3011,10 +3017,10 @@
         <v>60</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0.5</v>
@@ -3050,12 +3056,12 @@
         <v>5</v>
       </c>
       <c r="O52">
-        <v>0.4645833333333334</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3088,27 +3094,27 @@
         <v>0</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
-        <v>0.5000000000000001</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0.5</v>
@@ -3135,21 +3141,21 @@
         <v>0</v>
       </c>
       <c r="L54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O54">
-        <v>0.5000000000000001</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3182,27 +3188,27 @@
         <v>0</v>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
-        <v>0.5062500000000001</v>
+        <v>0.4885416666666666</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0.5</v>
@@ -3238,12 +3244,12 @@
         <v>5</v>
       </c>
       <c r="O56">
-        <v>0.5302083333333333</v>
+        <v>0.5062500000000001</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3255,16 +3261,16 @@
         <v>0.5</v>
       </c>
       <c r="E57">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -3279,24 +3285,24 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>0.4885416666666666</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0.5</v>
@@ -3323,42 +3329,42 @@
         <v>0</v>
       </c>
       <c r="L58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58">
-        <v>0.5062500000000001</v>
+        <v>0.4864583333333333</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0.5</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F59">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -3370,21 +3376,21 @@
         <v>0</v>
       </c>
       <c r="L59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O59">
-        <v>0.4875</v>
+        <v>0.5302083333333333</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -3417,21 +3423,21 @@
         <v>0</v>
       </c>
       <c r="L60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O60">
-        <v>0.4864583333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3473,12 +3479,12 @@
         <v>7</v>
       </c>
       <c r="O61">
-        <v>0.51875</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -3502,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -3514,18 +3520,18 @@
         <v>1</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62">
-        <v>0.503125</v>
+        <v>0.5239583333333333</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -3558,27 +3564,27 @@
         <v>0</v>
       </c>
       <c r="L63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O63">
-        <v>0.5</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0.5</v>
@@ -3587,7 +3593,7 @@
         <v>0.5</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
@@ -3605,21 +3611,21 @@
         <v>0</v>
       </c>
       <c r="L64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O64">
-        <v>0.4927083333333334</v>
+        <v>0.515625</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -3661,18 +3667,18 @@
         <v>6</v>
       </c>
       <c r="O65">
-        <v>0.4927083333333334</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0.5</v>
@@ -3681,7 +3687,7 @@
         <v>0.5</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
@@ -3690,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -3699,27 +3705,27 @@
         <v>0</v>
       </c>
       <c r="L66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66">
+        <v>2</v>
+      </c>
+      <c r="N66">
         <v>4</v>
       </c>
-      <c r="N66">
-        <v>7</v>
-      </c>
       <c r="O66">
-        <v>0.51875</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0.5</v>
@@ -3728,7 +3734,7 @@
         <v>0.5</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
@@ -3752,15 +3758,15 @@
         <v>3</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O67">
-        <v>0.503125</v>
+        <v>0.4916666666666666</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -3802,12 +3808,12 @@
         <v>6</v>
       </c>
       <c r="O68">
-        <v>0.5</v>
+        <v>0.509375</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -3840,24 +3846,24 @@
         <v>0</v>
       </c>
       <c r="L69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O69">
-        <v>0.4927083333333334</v>
+        <v>0.503125</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -3869,7 +3875,7 @@
         <v>0.5</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -3887,27 +3893,27 @@
         <v>0</v>
       </c>
       <c r="L70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O70">
-        <v>0.4927083333333334</v>
+        <v>0.5104166666666667</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0.5</v>
@@ -3916,7 +3922,7 @@
         <v>0.5</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -3940,21 +3946,21 @@
         <v>2</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71">
-        <v>0.5083333333333333</v>
+        <v>0.5177083333333334</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0.5</v>
@@ -3990,12 +3996,12 @@
         <v>4</v>
       </c>
       <c r="O72">
-        <v>0.515625</v>
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -4037,18 +4043,18 @@
         <v>6</v>
       </c>
       <c r="O73">
-        <v>0.521875</v>
+        <v>0.4802083333333333</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0.5</v>
@@ -4057,7 +4063,7 @@
         <v>0.5</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
@@ -4075,27 +4081,27 @@
         <v>0</v>
       </c>
       <c r="L74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O74">
-        <v>0.4927083333333333</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0.5</v>
@@ -4104,7 +4110,7 @@
         <v>0.5</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
@@ -4113,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -4125,18 +4131,18 @@
         <v>1</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O75">
-        <v>0.4916666666666666</v>
+        <v>0.521875</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -4169,27 +4175,27 @@
         <v>0</v>
       </c>
       <c r="L76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O76">
-        <v>0.509375</v>
+        <v>0.4927083333333333</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0.5</v>
@@ -4198,7 +4204,7 @@
         <v>0.5</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
@@ -4207,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -4216,27 +4222,27 @@
         <v>0</v>
       </c>
       <c r="L77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N77">
         <v>5</v>
       </c>
       <c r="O77">
-        <v>0.503125</v>
+        <v>0.5052083333333334</v>
       </c>
     </row>
     <row r="78" spans="1:15">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0.5</v>
@@ -4263,21 +4269,21 @@
         <v>0</v>
       </c>
       <c r="L78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O78">
-        <v>0.5104166666666667</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -4310,24 +4316,24 @@
         <v>0</v>
       </c>
       <c r="L79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O79">
-        <v>0.5177083333333334</v>
+        <v>0.4989583333333334</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -4339,7 +4345,7 @@
         <v>0.5</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
@@ -4357,391 +4363,15 @@
         <v>0</v>
       </c>
       <c r="L80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O80">
-        <v>0.4958333333333333</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
-      <c r="A81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>0.5</v>
-      </c>
-      <c r="E81">
-        <v>0.5</v>
-      </c>
-      <c r="F81">
-        <v>3</v>
-      </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" t="b">
-        <v>1</v>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="b">
-        <v>0</v>
-      </c>
-      <c r="L81" t="b">
-        <v>1</v>
-      </c>
-      <c r="M81">
-        <v>3</v>
-      </c>
-      <c r="N81">
-        <v>6</v>
-      </c>
-      <c r="O81">
-        <v>0.4802083333333333</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
-      <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>0.5</v>
-      </c>
-      <c r="E82">
-        <v>0.5</v>
-      </c>
-      <c r="F82">
-        <v>3</v>
-      </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" t="b">
-        <v>1</v>
-      </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82" t="b">
-        <v>1</v>
-      </c>
-      <c r="M82">
-        <v>3</v>
-      </c>
-      <c r="N82">
-        <v>6</v>
-      </c>
-      <c r="O82">
-        <v>0.521875</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
-      <c r="A83" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>0.5</v>
-      </c>
-      <c r="E83">
-        <v>0.5</v>
-      </c>
-      <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M83">
-        <v>4</v>
-      </c>
-      <c r="N83">
-        <v>7</v>
-      </c>
-      <c r="O83">
-        <v>0.521875</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
-      <c r="A84" t="s">
-        <v>82</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>0.5</v>
-      </c>
-      <c r="E84">
-        <v>0.5</v>
-      </c>
-      <c r="F84">
-        <v>3</v>
-      </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" t="b">
-        <v>1</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>2</v>
-      </c>
-      <c r="N84">
-        <v>5</v>
-      </c>
-      <c r="O84">
-        <v>0.4927083333333333</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
-      <c r="A85" t="s">
-        <v>83</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
-        <v>0.5</v>
-      </c>
-      <c r="E85">
-        <v>0.5</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" t="b">
-        <v>1</v>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85" t="b">
-        <v>1</v>
-      </c>
-      <c r="M85">
-        <v>4</v>
-      </c>
-      <c r="N85">
-        <v>5</v>
-      </c>
-      <c r="O85">
-        <v>0.5052083333333334</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
-      <c r="A86" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <v>0.5</v>
-      </c>
-      <c r="E86">
-        <v>0.5</v>
-      </c>
-      <c r="F86">
-        <v>2</v>
-      </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" t="b">
-        <v>1</v>
-      </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86" t="b">
-        <v>1</v>
-      </c>
-      <c r="M86">
-        <v>3</v>
-      </c>
-      <c r="N86">
-        <v>5</v>
-      </c>
-      <c r="O86">
-        <v>0.4875</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
-      <c r="A87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>0.5</v>
-      </c>
-      <c r="E87">
-        <v>0.5</v>
-      </c>
-      <c r="F87">
-        <v>2</v>
-      </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87" t="b">
-        <v>1</v>
-      </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87" t="b">
-        <v>1</v>
-      </c>
-      <c r="M87">
-        <v>3</v>
-      </c>
-      <c r="N87">
-        <v>5</v>
-      </c>
-      <c r="O87">
-        <v>0.4989583333333334</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>0.5</v>
-      </c>
-      <c r="E88">
-        <v>0.5</v>
-      </c>
-      <c r="F88">
-        <v>3</v>
-      </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" t="b">
-        <v>1</v>
-      </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-      <c r="L88" t="b">
-        <v>1</v>
-      </c>
-      <c r="M88">
-        <v>3</v>
-      </c>
-      <c r="N88">
-        <v>6</v>
-      </c>
-      <c r="O88">
         <v>0.5114583333333333</v>
       </c>
     </row>
